--- a/data/trans_orig/P6703-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6703-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>17294</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29580</t>
+          <t>30093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39520</t>
+          <t>39735</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66272</t>
+          <t>68108</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26382</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49724</t>
+          <t>50136</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72650</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108247</t>
+          <t>108575</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89193</t>
+          <t>87744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121792</t>
+          <t>123333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45755</t>
+          <t>46381</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73767</t>
+          <t>72591</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142770</t>
+          <t>141821</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>186123</t>
+          <t>184958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111161</t>
+          <t>110712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147978</t>
+          <t>147192</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73902</t>
+          <t>73881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101748</t>
+          <t>101277</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191696</t>
+          <t>191959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>239446</t>
+          <t>238006</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12443</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15905</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23280</t>
+          <t>23079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39766</t>
+          <t>40758</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67238</t>
+          <t>67556</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22618</t>
+          <t>22665</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43628</t>
+          <t>43363</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69539</t>
+          <t>69925</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>105517</t>
+          <t>104242</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70085</t>
+          <t>70981</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101371</t>
+          <t>102868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38384</t>
+          <t>36982</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61755</t>
+          <t>62440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115650</t>
+          <t>113949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157630</t>
+          <t>154607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96599</t>
+          <t>96184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130082</t>
+          <t>130423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61904</t>
+          <t>61213</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88620</t>
+          <t>88812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>166817</t>
+          <t>166731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209389</t>
+          <t>210062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>16050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15170</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>21810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56944</t>
+          <t>55566</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85794</t>
+          <t>84590</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28066</t>
+          <t>27431</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>70841</t>
+          <t>71239</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>104221</t>
+          <t>106266</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68355</t>
+          <t>68220</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97666</t>
+          <t>97713</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23459</t>
+          <t>23110</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42721</t>
+          <t>41872</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95869</t>
+          <t>96561</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131202</t>
+          <t>131635</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>100827</t>
+          <t>100899</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134294</t>
+          <t>133160</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42262</t>
+          <t>42326</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63969</t>
+          <t>63873</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>151065</t>
+          <t>150725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>190183</t>
+          <t>190720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,61%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>17881</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>28193</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16750</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39833</t>
+          <t>38583</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24369</t>
+          <t>24227</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56312</t>
+          <t>56695</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88847</t>
+          <t>88514</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44397</t>
+          <t>44142</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71372</t>
+          <t>72629</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>108735</t>
+          <t>108052</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>149577</t>
+          <t>152521</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92077</t>
+          <t>94177</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>130749</t>
+          <t>130919</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70158</t>
+          <t>69923</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101009</t>
+          <t>100737</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171546</t>
+          <t>168037</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>219738</t>
+          <t>219054</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>206147</t>
+          <t>204228</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>248919</t>
+          <t>247169</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>116972</t>
+          <t>118647</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>151485</t>
+          <t>151979</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>338278</t>
+          <t>336679</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>392894</t>
+          <t>393245</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18107</t>
+          <t>17993</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17967</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15317</t>
+          <t>15410</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32402</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40782</t>
+          <t>40816</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39431</t>
+          <t>39388</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>66401</t>
+          <t>66295</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>33781</t>
+          <t>33430</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>57294</t>
+          <t>57016</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>42463</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>70354</t>
+          <t>68708</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>83157</t>
+          <t>83499</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>118614</t>
+          <t>118950</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>63282</t>
+          <t>63143</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>88062</t>
+          <t>89353</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>67324</t>
+          <t>67287</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>95353</t>
+          <t>95174</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>138682</t>
+          <t>137704</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>176050</t>
+          <t>176075</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,6%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>17753</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>40247</t>
+          <t>38948</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>43226</t>
+          <t>42850</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>42199</t>
+          <t>43342</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>75410</t>
+          <t>73677</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24167</t>
+          <t>22667</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>49097</t>
+          <t>46822</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>23543</t>
+          <t>23408</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>47785</t>
+          <t>46078</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>52717</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>84535</t>
+          <t>87411</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>239966</t>
+          <t>239989</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>299027</t>
+          <t>301776</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>147794</t>
+          <t>150646</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>198636</t>
+          <t>200046</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>406423</t>
+          <t>404977</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>482096</t>
+          <t>484093</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>393242</t>
+          <t>396048</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>467545</t>
+          <t>466308</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>248692</t>
+          <t>251447</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>306944</t>
+          <t>309988</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>664296</t>
+          <t>660794</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>757598</t>
+          <t>755024</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>617714</t>
+          <t>621850</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>697278</t>
+          <t>699229</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>397847</t>
+          <t>400927</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>466188</t>
+          <t>463240</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1043574</t>
+          <t>1043749</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1144173</t>
+          <t>1142433</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>21084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10769</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>28382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18746</t>
+          <t>17291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>18092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>38884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29597</t>
+          <t>29536</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52966</t>
+          <t>53043</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>27831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50114</t>
+          <t>50551</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63128</t>
+          <t>63411</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96586</t>
+          <t>95668</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79605</t>
+          <t>78757</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112728</t>
+          <t>112563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>55869</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80200</t>
+          <t>82210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143124</t>
+          <t>141390</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>184428</t>
+          <t>184626</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99692</t>
+          <t>101115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133614</t>
+          <t>134798</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78581</t>
+          <t>77857</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107255</t>
+          <t>108250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186584</t>
+          <t>188347</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>234004</t>
+          <t>233535</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17948</t>
+          <t>17416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>11373</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30828</t>
+          <t>28902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9707</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>24199</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>17971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39045</t>
+          <t>40231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32709</t>
+          <t>32428</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59251</t>
+          <t>57950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45652</t>
+          <t>45099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62246</t>
+          <t>61239</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>96031</t>
+          <t>96578</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71620</t>
+          <t>70034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101543</t>
+          <t>102314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48593</t>
+          <t>48145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74465</t>
+          <t>75519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127952</t>
+          <t>129130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168080</t>
+          <t>167629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78395</t>
+          <t>78203</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109688</t>
+          <t>109646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54489</t>
+          <t>55637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81739</t>
+          <t>82397</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143899</t>
+          <t>141189</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183553</t>
+          <t>182891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>12792</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>21827</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24459</t>
+          <t>23303</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38950</t>
+          <t>38939</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63768</t>
+          <t>64742</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>15449</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46637</t>
+          <t>46312</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74330</t>
+          <t>73132</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70326</t>
+          <t>70475</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98891</t>
+          <t>100375</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16583</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31821</t>
+          <t>31594</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93751</t>
+          <t>91900</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126014</t>
+          <t>125556</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,14%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48727</t>
+          <t>49655</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>76683</t>
+          <t>77529</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23179</t>
+          <t>23036</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39811</t>
+          <t>39038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78150</t>
+          <t>78829</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109399</t>
+          <t>112659</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24068</t>
+          <t>24066</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>16703</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36788</t>
+          <t>36478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29490</t>
+          <t>29920</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>15959</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34090</t>
+          <t>35645</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31031</t>
+          <t>31824</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57119</t>
+          <t>58262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>76498</t>
+          <t>77636</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>112702</t>
+          <t>113177</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43577</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71572</t>
+          <t>70899</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>127846</t>
+          <t>127519</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>172629</t>
+          <t>171071</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>123623</t>
+          <t>123224</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>162990</t>
+          <t>163024</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>82903</t>
+          <t>82286</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114567</t>
+          <t>113509</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>216377</t>
+          <t>215202</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>269340</t>
+          <t>267274</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>196765</t>
+          <t>196338</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>240505</t>
+          <t>239695</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161649</t>
+          <t>162428</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>197858</t>
+          <t>199046</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>365098</t>
+          <t>368338</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>427597</t>
+          <t>429790</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,16%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>10815</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>21040</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13633</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32284</t>
+          <t>30739</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>31586</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54935</t>
+          <t>55636</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>27474</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49374</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>64027</t>
+          <t>64622</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>95611</t>
+          <t>96511</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>44522</t>
+          <t>44261</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>71849</t>
+          <t>69865</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>47015</t>
+          <t>49262</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>73974</t>
+          <t>73975</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>100383</t>
+          <t>99823</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>135466</t>
+          <t>138527</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>65234</t>
+          <t>65883</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>93919</t>
+          <t>93749</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>69030</t>
+          <t>70200</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>96863</t>
+          <t>97860</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>142206</t>
+          <t>140828</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>180220</t>
+          <t>181420</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>29794</t>
+          <t>29198</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>56535</t>
+          <t>54754</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>25815</t>
+          <t>24484</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>51571</t>
+          <t>49089</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>60396</t>
+          <t>61561</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>95540</t>
+          <t>95208</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>58898</t>
+          <t>57991</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>94908</t>
+          <t>92533</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>45867</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>76781</t>
+          <t>77660</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>112637</t>
+          <t>113116</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>158821</t>
+          <t>160943</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>241635</t>
+          <t>242647</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>302758</t>
+          <t>303751</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>149860</t>
+          <t>147561</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>198427</t>
+          <t>197833</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>404620</t>
+          <t>403594</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>481172</t>
+          <t>482341</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>432259</t>
+          <t>428687</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>503993</t>
+          <t>503720</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>283239</t>
+          <t>280350</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>341994</t>
+          <t>341080</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>729303</t>
+          <t>729968</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>825007</t>
+          <t>819597</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>531787</t>
+          <t>533444</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>607872</t>
+          <t>610094</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>420141</t>
+          <t>423729</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>486996</t>
+          <t>489488</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>976475</t>
+          <t>980177</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1079664</t>
+          <t>1080073</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -9377,32 +9377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19703</t>
+          <t>24594</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9447,32 +9447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12801</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>27295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9500,12 +9500,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9525,32 +9525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9560,32 +9560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -9603,32 +9603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15258</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23934</t>
+          <t>26515</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9638,32 +9638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21998</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9673,32 +9673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>29873</t>
+          <t>33270</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>24369</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39320</t>
+          <t>43817</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -9716,32 +9716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14460</t>
+          <t>16135</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31629</t>
+          <t>34455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9751,32 +9751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>22234</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28397</t>
+          <t>30383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9786,32 +9786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>43612</t>
+          <t>47328</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33754</t>
+          <t>35702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55405</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -9829,32 +9829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>37512</t>
+          <t>41403</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26921</t>
+          <t>31077</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47816</t>
+          <t>53304</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9864,32 +9864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41732</t>
+          <t>43687</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34061</t>
+          <t>34419</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50392</t>
+          <t>51534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9899,32 +9899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>79244</t>
+          <t>85091</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66715</t>
+          <t>70720</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91658</t>
+          <t>98795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -9942,17 +9942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9977,17 +9977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10012,17 +10012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10059,32 +10059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10094,32 +10094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>12894</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10129,32 +10129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -10172,32 +10172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>13211</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10207,32 +10207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10242,32 +10242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -10285,32 +10285,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23303</t>
+          <t>23588</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10320,32 +10320,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7123</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10355,32 +10355,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>27164</t>
+          <t>27149</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>18488</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36660</t>
+          <t>36542</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -10398,32 +10398,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12313</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27733</t>
+          <t>31198</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10433,32 +10433,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>23676</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10468,32 +10468,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>34720</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24849</t>
+          <t>28409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45583</t>
+          <t>50481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -10511,32 +10511,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23305</t>
+          <t>25910</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>34479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10546,32 +10546,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26297</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19508</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>36377</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10581,32 +10581,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>49602</t>
+          <t>54375</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38944</t>
+          <t>43294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60930</t>
+          <t>66715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -10624,17 +10624,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10659,17 +10659,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10694,17 +10694,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>482</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14650</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -10854,67 +10854,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10427</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28201</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5786</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4368</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10924,32 +10924,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26477</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -10967,32 +10967,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20736</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114276</t>
+          <t>31266</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11002,32 +11002,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>98656</t>
+          <t>34421</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -11080,32 +11080,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78779</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11115,32 +11115,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11150,32 +11150,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23389</t>
+          <t>27238</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>17884</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99989</t>
+          <t>38586</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -11193,32 +11193,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>268541</t>
+          <t>26541</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98507</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>303040</t>
+          <t>37161</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11228,32 +11228,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16144</t>
+          <t>17061</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11263,32 +11263,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>279859</t>
+          <t>38807</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>120072</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>324382</t>
+          <t>50267</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -11306,17 +11306,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11341,17 +11341,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11376,17 +11376,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11423,32 +11423,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11458,32 +11458,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>10763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11493,27 +11493,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15458</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -11536,32 +11536,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16420</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11571,32 +11571,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11606,32 +11606,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24031</t>
+          <t>23918</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -11649,32 +11649,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>21135</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26533</t>
+          <t>32032</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11684,32 +11684,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24137</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11719,32 +11719,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>33657</t>
+          <t>40948</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>30548</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45833</t>
+          <t>54416</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -11762,32 +11762,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33653</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>23041</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44965</t>
+          <t>46479</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11797,32 +11797,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28199</t>
+          <t>31640</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36783</t>
+          <t>41042</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11832,32 +11832,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>60924</t>
+          <t>65293</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48203</t>
+          <t>52521</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>75195</t>
+          <t>81463</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -11875,32 +11875,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>62728</t>
+          <t>67958</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>49727</t>
+          <t>54488</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>74748</t>
+          <t>81071</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11910,32 +11910,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>49819</t>
+          <t>54507</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40656</t>
+          <t>44768</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59573</t>
+          <t>64563</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11945,32 +11945,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>112548</t>
+          <t>122465</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>97538</t>
+          <t>106152</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>127891</t>
+          <t>139692</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -11988,17 +11988,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12023,17 +12023,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>106232</t>
+          <t>118281</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>106232</t>
+          <t>118281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106232</t>
+          <t>118281</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12058,17 +12058,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>229973</t>
+          <t>252743</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>229973</t>
+          <t>252743</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>229973</t>
+          <t>252743</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12140,32 +12140,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12175,32 +12175,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>15684</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -12218,32 +12218,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14194</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12253,32 +12253,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12288,32 +12288,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9364</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -12331,32 +12331,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>16177</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>26550</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12366,32 +12366,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20757</t>
+          <t>24516</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12401,32 +12401,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>25097</t>
+          <t>33999</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17810</t>
+          <t>23892</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>34883</t>
+          <t>46371</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -12444,32 +12444,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>19999</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32474</t>
+          <t>32451</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12479,32 +12479,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>17625</t>
+          <t>21217</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24223</t>
+          <t>29032</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12514,32 +12514,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>37624</t>
+          <t>41624</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>27212</t>
+          <t>30434</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>52611</t>
+          <t>54670</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -12557,32 +12557,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>34494</t>
+          <t>48067</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23942</t>
+          <t>35215</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>45566</t>
+          <t>60105</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12592,32 +12592,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>36396</t>
+          <t>43609</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>36022</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>52328</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12627,32 +12627,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>70890</t>
+          <t>91676</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>57242</t>
+          <t>75268</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>83229</t>
+          <t>106568</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -12670,17 +12670,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12705,17 +12705,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12740,17 +12740,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12787,32 +12787,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>23087</t>
+          <t>28747</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>42592</t>
+          <t>42646</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12822,32 +12822,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>12132</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23440</t>
+          <t>27417</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12857,32 +12857,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>47199</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>35237</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>56771</t>
+          <t>64441</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -12900,32 +12900,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>26933</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>50079</t>
+          <t>39805</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12935,32 +12935,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>25113</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12970,32 +12970,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>42534</t>
+          <t>44131</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>31613</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>63522</t>
+          <t>58915</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -13013,32 +13013,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>78677</t>
+          <t>90132</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>30156</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>133287</t>
+          <t>112558</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13048,32 +13048,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>61821</t>
+          <t>69982</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>50229</t>
+          <t>58579</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>73674</t>
+          <t>84720</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13083,32 +13083,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>140498</t>
+          <t>160114</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>71689</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>193265</t>
+          <t>184277</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -13126,32 +13126,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>109047</t>
+          <t>117838</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>40753</t>
+          <t>97686</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>185968</t>
+          <t>140471</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13161,32 +13161,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>91221</t>
+          <t>101782</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>77062</t>
+          <t>85321</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>107104</t>
+          <t>117351</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13196,32 +13196,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>200268</t>
+          <t>219620</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>103024</t>
+          <t>193079</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>274561</t>
+          <t>248192</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -13239,32 +13239,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>426581</t>
+          <t>209881</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>274493</t>
+          <t>183020</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>571667</t>
+          <t>235278</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13274,32 +13274,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>165562</t>
+          <t>182535</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>147880</t>
+          <t>165121</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>182638</t>
+          <t>201274</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13309,32 +13309,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>592143</t>
+          <t>392415</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>444491</t>
+          <t>362121</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>808725</t>
+          <t>426039</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>49,34%</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13352,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13387,17 +13387,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>349588</t>
+          <t>389612</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>349588</t>
+          <t>389612</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>349588</t>
+          <t>389612</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13422,17 +13422,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1013914</t>
+          <t>863480</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1013914</t>
+          <t>863480</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1013914</t>
+          <t>863480</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
